--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/49.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/49.xlsx
@@ -426,13 +426,13 @@
         <v>-0.639345853198962</v>
       </c>
       <c r="E2">
-        <v>-6.131170962802614</v>
+        <v>-8.952591408541554</v>
       </c>
       <c r="F2">
-        <v>-7.939843736436551</v>
+        <v>-8.427593088347113</v>
       </c>
       <c r="G2">
-        <v>-6.028733005323375</v>
+        <v>-7.827514613540836</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-0.08951745013977841</v>
       </c>
       <c r="E3">
-        <v>-5.309189531774337</v>
+        <v>-9.555621121298969</v>
       </c>
       <c r="F3">
-        <v>-8.014401839450088</v>
+        <v>-7.793095566679537</v>
       </c>
       <c r="G3">
-        <v>-6.198580544215684</v>
+        <v>-7.377657822391431</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>0.3216163447146305</v>
       </c>
       <c r="E4">
-        <v>-6.229248652860739</v>
+        <v>-8.780944129754817</v>
       </c>
       <c r="F4">
-        <v>-8.157232316698783</v>
+        <v>-7.650413165933935</v>
       </c>
       <c r="G4">
-        <v>-6.53182336874426</v>
+        <v>-7.883830303709377</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>0.5229470755706116</v>
       </c>
       <c r="E5">
-        <v>-6.233922038036654</v>
+        <v>-9.250130264741527</v>
       </c>
       <c r="F5">
-        <v>-7.938163820386748</v>
+        <v>-7.643481681068536</v>
       </c>
       <c r="G5">
-        <v>-6.444325650141323</v>
+        <v>-8.167914837525316</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>0.5568520055968087</v>
       </c>
       <c r="E6">
-        <v>-6.662605501498761</v>
+        <v>-9.986079746572083</v>
       </c>
       <c r="F6">
-        <v>-7.88108032844417</v>
+        <v>-7.546964307757994</v>
       </c>
       <c r="G6">
-        <v>-6.606082215735652</v>
+        <v>-9.851794031165753</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>0.4497249909298776</v>
       </c>
       <c r="E7">
-        <v>-8.342298023475834</v>
+        <v>-11.25100480571262</v>
       </c>
       <c r="F7">
-        <v>-7.640937853441861</v>
+        <v>-7.697282150648408</v>
       </c>
       <c r="G7">
-        <v>-7.141976774905176</v>
+        <v>-8.828428262429625</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>0.251571661954375</v>
       </c>
       <c r="E8">
-        <v>-8.796205087160665</v>
+        <v>-12.66112632696109</v>
       </c>
       <c r="F8">
-        <v>-7.490384038370046</v>
+        <v>-7.369003669966542</v>
       </c>
       <c r="G8">
-        <v>-7.137080478052594</v>
+        <v>-10.02138003696046</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>0.007949621962452323</v>
       </c>
       <c r="E9">
-        <v>-9.717966914473951</v>
+        <v>-12.45896166183667</v>
       </c>
       <c r="F9">
-        <v>-7.518417612705719</v>
+        <v>-6.989245640723881</v>
       </c>
       <c r="G9">
-        <v>-7.853846692760198</v>
+        <v>-10.06058351723651</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-0.2305916496608671</v>
       </c>
       <c r="E10">
-        <v>-10.12094675946852</v>
+        <v>-14.21034898430318</v>
       </c>
       <c r="F10">
-        <v>-7.520284010127065</v>
+        <v>-7.121384519337444</v>
       </c>
       <c r="G10">
-        <v>-8.123368136748883</v>
+        <v>-9.671081281813557</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-0.4252625203007797</v>
       </c>
       <c r="E11">
-        <v>-10.67547651560379</v>
+        <v>-13.39470288841163</v>
       </c>
       <c r="F11">
-        <v>-6.994277470343711</v>
+        <v>-7.126429810457555</v>
       </c>
       <c r="G11">
-        <v>-8.324023612429649</v>
+        <v>-10.49239452465135</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-0.5469389730500345</v>
       </c>
       <c r="E12">
-        <v>-11.21974927811168</v>
+        <v>-14.38737156173702</v>
       </c>
       <c r="F12">
-        <v>-6.632640996038464</v>
+        <v>-7.227500338274986</v>
       </c>
       <c r="G12">
-        <v>-7.44761627072731</v>
+        <v>-10.62933193033776</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-0.5835082149612633</v>
       </c>
       <c r="E13">
-        <v>-10.83954312890168</v>
+        <v>-12.74772886388378</v>
       </c>
       <c r="F13">
-        <v>-6.839217220089513</v>
+        <v>-6.920641876025917</v>
       </c>
       <c r="G13">
-        <v>-8.211849087376985</v>
+        <v>-10.34935247299052</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-0.5380152759998356</v>
       </c>
       <c r="E14">
-        <v>-11.71469790172803</v>
+        <v>-15.35401962341433</v>
       </c>
       <c r="F14">
-        <v>-6.702198151697523</v>
+        <v>-6.876256142186853</v>
       </c>
       <c r="G14">
-        <v>-7.410915562878949</v>
+        <v>-9.330475804005641</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-0.4288850857872997</v>
       </c>
       <c r="E15">
-        <v>-12.14022049033278</v>
+        <v>-15.38808280490003</v>
       </c>
       <c r="F15">
-        <v>-6.44762851173204</v>
+        <v>-6.556657953627511</v>
       </c>
       <c r="G15">
-        <v>-6.733803062640735</v>
+        <v>-9.44403413709372</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.2858926263799167</v>
       </c>
       <c r="E16">
-        <v>-13.0336612412021</v>
+        <v>-15.78394841722855</v>
       </c>
       <c r="F16">
-        <v>-6.044246737275247</v>
+        <v>-6.404541020817158</v>
       </c>
       <c r="G16">
-        <v>-6.950120729267793</v>
+        <v>-8.881943231071944</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.1433205089461576</v>
       </c>
       <c r="E17">
-        <v>-13.35270582046449</v>
+        <v>-16.70479096431828</v>
       </c>
       <c r="F17">
-        <v>-5.62798309890227</v>
+        <v>-5.956645628268629</v>
       </c>
       <c r="G17">
-        <v>-6.659971276023909</v>
+        <v>-8.340450539395514</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.03732288193556655</v>
       </c>
       <c r="E18">
-        <v>-13.71831669794777</v>
+        <v>-17.44689464232526</v>
       </c>
       <c r="F18">
-        <v>-5.676150722467402</v>
+        <v>-6.178016832981713</v>
       </c>
       <c r="G18">
-        <v>-6.429981056319661</v>
+        <v>-8.028852061602691</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.003403455469780137</v>
       </c>
       <c r="E19">
-        <v>-16.31778757562277</v>
+        <v>-18.18044403293175</v>
       </c>
       <c r="F19">
-        <v>-5.361635438043663</v>
+        <v>-5.676801625598648</v>
       </c>
       <c r="G19">
-        <v>-5.535710010887414</v>
+        <v>-8.363822990902769</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.0407429212803109</v>
       </c>
       <c r="E20">
-        <v>-14.53616816068105</v>
+        <v>-19.39119948599253</v>
       </c>
       <c r="F20">
-        <v>-5.150793502109378</v>
+        <v>-5.699150091624372</v>
       </c>
       <c r="G20">
-        <v>-5.215785511063324</v>
+        <v>-7.571318115347717</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.1769901678421228</v>
       </c>
       <c r="E21">
-        <v>-16.00123365706459</v>
+        <v>-19.74705150198928</v>
       </c>
       <c r="F21">
-        <v>-4.604711114288956</v>
+        <v>-5.061307783063389</v>
       </c>
       <c r="G21">
-        <v>-5.105984647162317</v>
+        <v>-8.224495371337001</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.3978126272583217</v>
       </c>
       <c r="E22">
-        <v>-15.76702098138788</v>
+        <v>-19.42096967411896</v>
       </c>
       <c r="F22">
-        <v>-4.294040275974947</v>
+        <v>-4.600398683081215</v>
       </c>
       <c r="G22">
-        <v>-5.638085321143836</v>
+        <v>-6.208594944471979</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.684641363540347</v>
       </c>
       <c r="E23">
-        <v>-16.72892773077916</v>
+        <v>-21.81403723499835</v>
       </c>
       <c r="F23">
-        <v>-4.320176966550402</v>
+        <v>-4.771282926916005</v>
       </c>
       <c r="G23">
-        <v>-4.580031656247225</v>
+        <v>-7.828898421576251</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.008716597303155</v>
       </c>
       <c r="E24">
-        <v>-17.59986649430436</v>
+        <v>-21.4489109042339</v>
       </c>
       <c r="F24">
-        <v>-4.068646458236646</v>
+        <v>-4.647296966355123</v>
       </c>
       <c r="G24">
-        <v>-5.412597443372997</v>
+        <v>-7.239790153408483</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.336170450566944</v>
       </c>
       <c r="E25">
-        <v>-17.5090887043466</v>
+        <v>-21.27031694631939</v>
       </c>
       <c r="F25">
-        <v>-4.114284111601865</v>
+        <v>-4.154673363563317</v>
       </c>
       <c r="G25">
-        <v>-5.906971140388981</v>
+        <v>-8.29644676808752</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.630280979687146</v>
       </c>
       <c r="E26">
-        <v>-16.33998615520837</v>
+        <v>-21.10798473856643</v>
       </c>
       <c r="F26">
-        <v>-3.831931518761828</v>
+        <v>-4.437732289241641</v>
       </c>
       <c r="G26">
-        <v>-6.04951661021892</v>
+        <v>-8.530363294801344</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.856702008801059</v>
       </c>
       <c r="E27">
-        <v>-18.19918738684949</v>
+        <v>-21.65741543296906</v>
       </c>
       <c r="F27">
-        <v>-4.186854267765047</v>
+        <v>-4.208101266326582</v>
       </c>
       <c r="G27">
-        <v>-6.650294551412619</v>
+        <v>-8.515704199153451</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.985815226177177</v>
       </c>
       <c r="E28">
-        <v>-18.41330722335417</v>
+        <v>-21.65828037150453</v>
       </c>
       <c r="F28">
-        <v>-3.548007097800717</v>
+        <v>-4.161853094330962</v>
       </c>
       <c r="G28">
-        <v>-6.723401328556345</v>
+        <v>-8.554493861237091</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.994003049739507</v>
       </c>
       <c r="E29">
-        <v>-17.63974423641591</v>
+        <v>-22.98599272276142</v>
       </c>
       <c r="F29">
-        <v>-3.767734415773574</v>
+        <v>-3.929229659088681</v>
       </c>
       <c r="G29">
-        <v>-6.488382390177944</v>
+        <v>-8.459385198439369</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.869249156843279</v>
       </c>
       <c r="E30">
-        <v>-17.34072004074142</v>
+        <v>-20.7082744518054</v>
       </c>
       <c r="F30">
-        <v>-3.771958159450052</v>
+        <v>-3.732325127063222</v>
       </c>
       <c r="G30">
-        <v>-7.110228643183565</v>
+        <v>-8.332164243910718</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.605096149625181</v>
       </c>
       <c r="E31">
-        <v>-17.45266391821103</v>
+        <v>-21.01103463853622</v>
       </c>
       <c r="F31">
-        <v>-3.741413223458971</v>
+        <v>-3.754708434619085</v>
       </c>
       <c r="G31">
-        <v>-6.616934184013384</v>
+        <v>-8.853211006336609</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.205593247644866</v>
       </c>
       <c r="E32">
-        <v>-16.72471172147802</v>
+        <v>-21.19581902041921</v>
       </c>
       <c r="F32">
-        <v>-3.430913425383828</v>
+        <v>-4.208155904180665</v>
       </c>
       <c r="G32">
-        <v>-6.767848712966599</v>
+        <v>-8.292315207254511</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.6838392543903458</v>
       </c>
       <c r="E33">
-        <v>-17.02673376694559</v>
+        <v>-21.61585762700067</v>
       </c>
       <c r="F33">
-        <v>-3.985665019385366</v>
+        <v>-4.33814490201402</v>
       </c>
       <c r="G33">
-        <v>-5.767643520823214</v>
+        <v>-7.998610228101449</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.05344715525086528</v>
       </c>
       <c r="E34">
-        <v>-16.86384908536369</v>
+        <v>-20.40725772756754</v>
       </c>
       <c r="F34">
-        <v>-3.620610511788123</v>
+        <v>-4.041865991206565</v>
       </c>
       <c r="G34">
-        <v>-6.077762184759981</v>
+        <v>-8.302925505707874</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.6611309850831303</v>
       </c>
       <c r="E35">
-        <v>-16.18953666325154</v>
+        <v>-18.88991552723946</v>
       </c>
       <c r="F35">
-        <v>-3.651008954982025</v>
+        <v>-4.548074623341011</v>
       </c>
       <c r="G35">
-        <v>-6.390092293116982</v>
+        <v>-7.701104742669305</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.434257063108978</v>
       </c>
       <c r="E36">
-        <v>-15.3550657009101</v>
+        <v>-20.91592762742713</v>
       </c>
       <c r="F36">
-        <v>-3.878072790608156</v>
+        <v>-4.733505206009112</v>
       </c>
       <c r="G36">
-        <v>-5.940626146341212</v>
+        <v>-7.291189683451207</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>2.240894251814653</v>
       </c>
       <c r="E37">
-        <v>-15.97149516825622</v>
+        <v>-20.0534163540302</v>
       </c>
       <c r="F37">
-        <v>-4.179680871821064</v>
+        <v>-4.180706321401311</v>
       </c>
       <c r="G37">
-        <v>-5.956933893667662</v>
+        <v>-8.055442363374118</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>3.049675484594974</v>
       </c>
       <c r="E38">
-        <v>-15.37580611186523</v>
+        <v>-19.81698019761572</v>
       </c>
       <c r="F38">
-        <v>-3.758145076455588</v>
+        <v>-3.993335698986797</v>
       </c>
       <c r="G38">
-        <v>-5.585255635428147</v>
+        <v>-7.00873062749505</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>3.840852112131935</v>
       </c>
       <c r="E39">
-        <v>-14.93357345417218</v>
+        <v>-18.51143019815238</v>
       </c>
       <c r="F39">
-        <v>-4.04390976369044</v>
+        <v>-4.448887913709996</v>
       </c>
       <c r="G39">
-        <v>-5.221473028299792</v>
+        <v>-7.709546633794446</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>4.595391229008789</v>
       </c>
       <c r="E40">
-        <v>-14.30764777683198</v>
+        <v>-19.10046692622609</v>
       </c>
       <c r="F40">
-        <v>-3.687141997295734</v>
+        <v>-3.957237498203228</v>
       </c>
       <c r="G40">
-        <v>-4.950498254819367</v>
+        <v>-6.319130749482705</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>5.29600794837758</v>
       </c>
       <c r="E41">
-        <v>-14.77066160174624</v>
+        <v>-18.80394244820383</v>
       </c>
       <c r="F41">
-        <v>-4.178632458505043</v>
+        <v>-4.174658940363205</v>
       </c>
       <c r="G41">
-        <v>-5.289286243126224</v>
+        <v>-6.253932865632298</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>5.935543865029592</v>
       </c>
       <c r="E42">
-        <v>-13.99588498377392</v>
+        <v>-18.70515831620051</v>
       </c>
       <c r="F42">
-        <v>-4.022830637955941</v>
+        <v>-4.488052169145856</v>
       </c>
       <c r="G42">
-        <v>-5.124795166916456</v>
+        <v>-6.435029638267049</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>6.50076793158622</v>
       </c>
       <c r="E43">
-        <v>-13.55632412574538</v>
+        <v>-18.2849113998147</v>
       </c>
       <c r="F43">
-        <v>-3.978134497757451</v>
+        <v>-4.437029123815186</v>
       </c>
       <c r="G43">
-        <v>-4.503872556116292</v>
+        <v>-6.136425051715867</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>6.98382238718582</v>
       </c>
       <c r="E44">
-        <v>-12.54339505970968</v>
+        <v>-17.61626862716014</v>
       </c>
       <c r="F44">
-        <v>-4.268430167616375</v>
+        <v>-4.331997747503241</v>
       </c>
       <c r="G44">
-        <v>-4.469396534870321</v>
+        <v>-6.508063583408911</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>7.378297198520193</v>
       </c>
       <c r="E45">
-        <v>-14.09205618627481</v>
+        <v>-16.67747973757802</v>
       </c>
       <c r="F45">
-        <v>-4.240833300186885</v>
+        <v>-4.31284678372079</v>
       </c>
       <c r="G45">
-        <v>-4.45441300575958</v>
+        <v>-5.557443742352729</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>7.676336490959902</v>
       </c>
       <c r="E46">
-        <v>-13.03735194751835</v>
+        <v>-18.00481169701826</v>
       </c>
       <c r="F46">
-        <v>-4.027227797430158</v>
+        <v>-4.153285245328434</v>
       </c>
       <c r="G46">
-        <v>-4.419811183783118</v>
+        <v>-5.92827781147973</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>7.880061799276788</v>
       </c>
       <c r="E47">
-        <v>-12.69961382755228</v>
+        <v>-18.19922814311557</v>
       </c>
       <c r="F47">
-        <v>-4.419453947418596</v>
+        <v>-4.131560759433394</v>
       </c>
       <c r="G47">
-        <v>-3.850579431033133</v>
+        <v>-6.188850850875766</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>7.98942535028791</v>
       </c>
       <c r="E48">
-        <v>-11.4558593843976</v>
+        <v>-16.73025910213742</v>
       </c>
       <c r="F48">
-        <v>-4.23764371647319</v>
+        <v>-4.635206163543701</v>
       </c>
       <c r="G48">
-        <v>-4.05536646754691</v>
+        <v>-6.489425212022814</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>8.008776704183671</v>
       </c>
       <c r="E49">
-        <v>-12.68735977688753</v>
+        <v>-16.5826534918574</v>
       </c>
       <c r="F49">
-        <v>-4.826106074590772</v>
+        <v>-4.917664864680073</v>
       </c>
       <c r="G49">
-        <v>-3.906484613554806</v>
+        <v>-5.686369627834106</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>7.94455592323901</v>
       </c>
       <c r="E50">
-        <v>-11.21827752405919</v>
+        <v>-15.52902250144075</v>
       </c>
       <c r="F50">
-        <v>-4.62724724946566</v>
+        <v>-4.999222551913373</v>
       </c>
       <c r="G50">
-        <v>-3.550822774634284</v>
+        <v>-6.070210830384904</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>7.801183001092906</v>
       </c>
       <c r="E51">
-        <v>-10.50478021635866</v>
+        <v>-16.22052048241202</v>
       </c>
       <c r="F51">
-        <v>-4.892460185035854</v>
+        <v>-4.914986026124106</v>
       </c>
       <c r="G51">
-        <v>-3.605052821113086</v>
+        <v>-5.38891711113059</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>7.585744645241254</v>
       </c>
       <c r="E52">
-        <v>-11.10463094036269</v>
+        <v>-15.87205440752178</v>
       </c>
       <c r="F52">
-        <v>-4.708185707686024</v>
+        <v>-4.431424388580445</v>
       </c>
       <c r="G52">
-        <v>-3.578389687339796</v>
+        <v>-5.744416733319687</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>7.300570892060192</v>
       </c>
       <c r="E53">
-        <v>-10.71313983392558</v>
+        <v>-15.4720769407943</v>
       </c>
       <c r="F53">
-        <v>-4.785240127148772</v>
+        <v>-5.195599709868992</v>
       </c>
       <c r="G53">
-        <v>-3.324530434297402</v>
+        <v>-5.780481816424508</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>6.952485205760968</v>
       </c>
       <c r="E54">
-        <v>-9.755802314808037</v>
+        <v>-15.54922402398897</v>
       </c>
       <c r="F54">
-        <v>-5.203156362644511</v>
+        <v>-5.158111807144625</v>
       </c>
       <c r="G54">
-        <v>-3.57664171929506</v>
+        <v>-5.760307351908189</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>6.547838060853569</v>
       </c>
       <c r="E55">
-        <v>-9.998216056912639</v>
+        <v>-14.07616124250789</v>
       </c>
       <c r="F55">
-        <v>-5.202954440140292</v>
+        <v>-5.261396355831839</v>
       </c>
       <c r="G55">
-        <v>-3.882880423859802</v>
+        <v>-5.362604895184463</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>6.092449191776501</v>
       </c>
       <c r="E56">
-        <v>-8.892833665536335</v>
+        <v>-14.52897241548286</v>
       </c>
       <c r="F56">
-        <v>-4.979630526033472</v>
+        <v>-5.543912070381166</v>
       </c>
       <c r="G56">
-        <v>-3.299747690390418</v>
+        <v>-5.299740945939242</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>5.598815384292167</v>
       </c>
       <c r="E57">
-        <v>-9.38788191558085</v>
+        <v>-12.77128598567168</v>
       </c>
       <c r="F57">
-        <v>-4.98915334970301</v>
+        <v>-5.392926299520916</v>
       </c>
       <c r="G57">
-        <v>-3.967299335111218</v>
+        <v>-4.983206444747367</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>5.0751065547678</v>
       </c>
       <c r="E58">
-        <v>-9.34490669724806</v>
+        <v>-14.54179252539858</v>
       </c>
       <c r="F58">
-        <v>-5.391113748100695</v>
+        <v>-5.163216091310086</v>
       </c>
       <c r="G58">
-        <v>-3.152785952811092</v>
+        <v>-6.084313754382199</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>4.534579368466542</v>
       </c>
       <c r="E59">
-        <v>-9.217765261008706</v>
+        <v>-13.86061040821679</v>
       </c>
       <c r="F59">
-        <v>-5.322993805559898</v>
+        <v>-5.475275839711936</v>
       </c>
       <c r="G59">
-        <v>-3.438866745587212</v>
+        <v>-6.117836338512859</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>3.991431916307223</v>
       </c>
       <c r="E60">
-        <v>-8.818906327361116</v>
+        <v>-12.29691474794619</v>
       </c>
       <c r="F60">
-        <v>-5.005270724804436</v>
+        <v>-5.370033830513239</v>
       </c>
       <c r="G60">
-        <v>-3.945989353474929</v>
+        <v>-6.218466991270086</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>3.455715839027601</v>
       </c>
       <c r="E61">
-        <v>-8.830005617153917</v>
+        <v>-13.67845254125825</v>
       </c>
       <c r="F61">
-        <v>-5.289419240152582</v>
+        <v>-5.534932457840624</v>
       </c>
       <c r="G61">
-        <v>-4.130337081829245</v>
+        <v>-5.535279639967309</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>2.945095686172257</v>
       </c>
       <c r="E62">
-        <v>-7.713483179718744</v>
+        <v>-13.18027058720042</v>
       </c>
       <c r="F62">
-        <v>-5.320128089705911</v>
+        <v>-5.74636432422841</v>
       </c>
       <c r="G62">
-        <v>-3.710450659446863</v>
+        <v>-6.428299299185711</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>2.472387859822775</v>
       </c>
       <c r="E63">
-        <v>-8.169971473587948</v>
+        <v>-12.82253472601649</v>
       </c>
       <c r="F63">
-        <v>-5.460516492432999</v>
+        <v>-5.31782617315782</v>
       </c>
       <c r="G63">
-        <v>-4.265255054736703</v>
+        <v>-6.613309136647882</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>2.048519977908519</v>
       </c>
       <c r="E64">
-        <v>-7.953130024204659</v>
+        <v>-14.03154671658432</v>
       </c>
       <c r="F64">
-        <v>-5.255809833215126</v>
+        <v>-5.675124481034198</v>
       </c>
       <c r="G64">
-        <v>-4.320243216143997</v>
+        <v>-6.846758876440668</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>1.68573915460255</v>
       </c>
       <c r="E65">
-        <v>-8.14360669791529</v>
+        <v>-14.22165205542632</v>
       </c>
       <c r="F65">
-        <v>-4.998478210133117</v>
+        <v>-5.536741049996056</v>
       </c>
       <c r="G65">
-        <v>-4.020562702292552</v>
+        <v>-7.430917879027226</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>1.389424738901581</v>
       </c>
       <c r="E66">
-        <v>-7.891157857409691</v>
+        <v>-13.35290054484682</v>
       </c>
       <c r="F66">
-        <v>-5.558918475782913</v>
+        <v>-5.364246177245265</v>
       </c>
       <c r="G66">
-        <v>-4.618126103767619</v>
+        <v>-6.755619557744532</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>1.166328138639373</v>
       </c>
       <c r="E67">
-        <v>-8.348723928092719</v>
+        <v>-14.28120148862719</v>
       </c>
       <c r="F67">
-        <v>-5.340912646140138</v>
+        <v>-5.550664992404601</v>
       </c>
       <c r="G67">
-        <v>-4.236344060542248</v>
+        <v>-6.761065405156633</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>1.021002573790254</v>
       </c>
       <c r="E68">
-        <v>-8.982008375695379</v>
+        <v>-13.03826217079389</v>
       </c>
       <c r="F68">
-        <v>-5.587947805212918</v>
+        <v>-5.672335574917109</v>
       </c>
       <c r="G68">
-        <v>-5.291789015553912</v>
+        <v>-6.639290298040081</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>0.9524180038436711</v>
       </c>
       <c r="E69">
-        <v>-8.905522449705828</v>
+        <v>-13.22488511312399</v>
       </c>
       <c r="F69">
-        <v>-5.534921371899217</v>
+        <v>-5.900734474629955</v>
       </c>
       <c r="G69">
-        <v>-4.776317211816153</v>
+        <v>-6.910642473711984</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>0.959764629372171</v>
       </c>
       <c r="E70">
-        <v>-8.264621108822265</v>
+        <v>-13.43045519070219</v>
       </c>
       <c r="F70">
-        <v>-5.156928778825791</v>
+        <v>-5.645700808831248</v>
       </c>
       <c r="G70">
-        <v>-4.414107113818953</v>
+        <v>-6.616215795631361</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>1.038873585459828</v>
       </c>
       <c r="E71">
-        <v>-8.87053093104856</v>
+        <v>-13.08264574454306</v>
       </c>
       <c r="F71">
-        <v>-5.503944876046178</v>
+        <v>-5.830906505259357</v>
       </c>
       <c r="G71">
-        <v>-4.727612465842395</v>
+        <v>-7.10067109821169</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>1.181217413637773</v>
       </c>
       <c r="E72">
-        <v>-9.372308493468474</v>
+        <v>-13.83229386024682</v>
       </c>
       <c r="F72">
-        <v>-5.383359132085746</v>
+        <v>-5.868259001127954</v>
       </c>
       <c r="G72">
-        <v>-4.559625453543157</v>
+        <v>-7.286468845512206</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>1.377076682476183</v>
       </c>
       <c r="E73">
-        <v>-8.737371152853012</v>
+        <v>-13.83024698999536</v>
       </c>
       <c r="F73">
-        <v>-5.372749094305259</v>
+        <v>-5.828597462034646</v>
       </c>
       <c r="G73">
-        <v>-4.599189783282988</v>
+        <v>-7.102935511360551</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>1.613721956927839</v>
       </c>
       <c r="E74">
-        <v>-8.993614854577039</v>
+        <v>-14.85279906329736</v>
       </c>
       <c r="F74">
-        <v>-5.707015567053402</v>
+        <v>-5.813530875808113</v>
       </c>
       <c r="G74">
-        <v>-4.237645104939181</v>
+        <v>-6.435748026649072</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>1.876423605070288</v>
       </c>
       <c r="E75">
-        <v>-10.02268793045009</v>
+        <v>-14.4028317719992</v>
       </c>
       <c r="F75">
-        <v>-5.807960190250554</v>
+        <v>-6.061248612130447</v>
       </c>
       <c r="G75">
-        <v>-4.577850006736846</v>
+        <v>-7.159479629171303</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>2.15188510356015</v>
       </c>
       <c r="E76">
-        <v>-10.4390947008774</v>
+        <v>-16.05274052042783</v>
       </c>
       <c r="F76">
-        <v>-5.791586254790826</v>
+        <v>-6.391776747065195</v>
       </c>
       <c r="G76">
-        <v>-4.28802829750135</v>
+        <v>-7.160813779023629</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>2.426421459129942</v>
       </c>
       <c r="E77">
-        <v>-10.32746781658833</v>
+        <v>-16.18415683613042</v>
       </c>
       <c r="F77">
-        <v>-5.867932757709373</v>
+        <v>-6.26215596085718</v>
       </c>
       <c r="G77">
-        <v>-4.080904015836848</v>
+        <v>-7.106560558726053</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>2.687077695005667</v>
       </c>
       <c r="E78">
-        <v>-11.10621590626538</v>
+        <v>-15.91891052807915</v>
       </c>
       <c r="F78">
-        <v>-5.904442722030956</v>
+        <v>-6.075727643462352</v>
       </c>
       <c r="G78">
-        <v>-4.106411769216932</v>
+        <v>-7.167408385737857</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>2.925203298931384</v>
       </c>
       <c r="E79">
-        <v>-11.75539982610897</v>
+        <v>-15.49549367988796</v>
       </c>
       <c r="F79">
-        <v>-6.253347388555506</v>
+        <v>-5.725270945140672</v>
       </c>
       <c r="G79">
-        <v>-4.24224014214769</v>
+        <v>-7.290117066696483</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>3.131809250794485</v>
       </c>
       <c r="E80">
-        <v>-12.31343462112617</v>
+        <v>-16.98552918194979</v>
       </c>
       <c r="F80">
-        <v>-5.902992047412414</v>
+        <v>-6.118397036015558</v>
       </c>
       <c r="G80">
-        <v>-4.541198957071575</v>
+        <v>-5.197666895326893</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>3.301010568239016</v>
       </c>
       <c r="E81">
-        <v>-11.96101065995323</v>
+        <v>-18.58852293965895</v>
       </c>
       <c r="F81">
-        <v>-6.292157289792786</v>
+        <v>-6.579139055023653</v>
       </c>
       <c r="G81">
-        <v>-4.719723435822313</v>
+        <v>-7.147462348863749</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>3.428004404523344</v>
       </c>
       <c r="E82">
-        <v>-13.7029878134318</v>
+        <v>-18.74462849565137</v>
       </c>
       <c r="F82">
-        <v>-6.161600533388746</v>
+        <v>-6.551615038066273</v>
       </c>
       <c r="G82">
-        <v>-3.945512634917274</v>
+        <v>-6.316985515973257</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>3.507584876712662</v>
       </c>
       <c r="E83">
-        <v>-15.2120746056439</v>
+        <v>-18.79889772815929</v>
       </c>
       <c r="F83">
-        <v>-5.943955392768213</v>
+        <v>-6.801698039173316</v>
       </c>
       <c r="G83">
-        <v>-4.304190380824071</v>
+        <v>-6.37501937927668</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>3.536379052394614</v>
       </c>
       <c r="E84">
-        <v>-15.04265986454295</v>
+        <v>-18.88330848366227</v>
       </c>
       <c r="F84">
-        <v>-6.162530564687589</v>
+        <v>-6.314445574993723</v>
       </c>
       <c r="G84">
-        <v>-4.407787282384485</v>
+        <v>-7.674259528891354</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>3.509911578530502</v>
       </c>
       <c r="E85">
-        <v>-15.8564175867733</v>
+        <v>-19.74574730147507</v>
       </c>
       <c r="F85">
-        <v>-6.365857816053113</v>
+        <v>-6.424770884254502</v>
       </c>
       <c r="G85">
-        <v>-3.666758079419561</v>
+        <v>-7.401695693552079</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>3.425911180839456</v>
       </c>
       <c r="E86">
-        <v>-17.63008500135755</v>
+        <v>-21.81008840566366</v>
       </c>
       <c r="F86">
-        <v>-6.428756676117184</v>
+        <v>-6.729625166667582</v>
       </c>
       <c r="G86">
-        <v>-3.885237532283763</v>
+        <v>-7.374151954665343</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>3.281402112235587</v>
       </c>
       <c r="E87">
-        <v>-18.83247636292617</v>
+        <v>-21.89635583550978</v>
       </c>
       <c r="F87">
-        <v>-6.473812713484958</v>
+        <v>-7.01194648131579</v>
       </c>
       <c r="G87">
-        <v>-3.170242459439669</v>
+        <v>-6.91847191391236</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>3.074175981556807</v>
       </c>
       <c r="E88">
-        <v>-19.93724741031143</v>
+        <v>-23.22850609129419</v>
       </c>
       <c r="F88">
-        <v>-6.152134327205686</v>
+        <v>-6.846529982154055</v>
       </c>
       <c r="G88">
-        <v>-3.439893014704385</v>
+        <v>-6.43339091822511</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>2.80419287162789</v>
       </c>
       <c r="E89">
-        <v>-20.87491323833965</v>
+        <v>-25.3462333755592</v>
       </c>
       <c r="F89">
-        <v>-6.672650158580212</v>
+        <v>-6.580154606441928</v>
       </c>
       <c r="G89">
-        <v>-5.171785050300872</v>
+        <v>-6.511741599503042</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>2.468898353471026</v>
       </c>
       <c r="E90">
-        <v>-22.90134195813603</v>
+        <v>-25.57018000066053</v>
       </c>
       <c r="F90">
-        <v>-6.652558473483989</v>
+        <v>-7.007565950753684</v>
       </c>
       <c r="G90">
-        <v>-4.075461478970285</v>
+        <v>-6.616003920716849</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>2.072248060965336</v>
       </c>
       <c r="E91">
-        <v>-23.704249456644</v>
+        <v>-28.33320577407056</v>
       </c>
       <c r="F91">
-        <v>-6.6527698982237</v>
+        <v>-6.720748099085065</v>
       </c>
       <c r="G91">
-        <v>-4.748614566743532</v>
+        <v>-6.466853912536063</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>1.616718454349089</v>
       </c>
       <c r="E92">
-        <v>-25.14654125724297</v>
+        <v>-29.18253465963116</v>
       </c>
       <c r="F92">
-        <v>-6.526146671387133</v>
+        <v>-6.21089694334511</v>
       </c>
       <c r="G92">
-        <v>-4.437608676602239</v>
+        <v>-7.123030522783927</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>1.105212662021556</v>
       </c>
       <c r="E93">
-        <v>-28.3938012847672</v>
+        <v>-29.61773006871629</v>
       </c>
       <c r="F93">
-        <v>-6.636715871358891</v>
+        <v>-5.927285304302297</v>
       </c>
       <c r="G93">
-        <v>-4.717293495396487</v>
+        <v>-7.615335128837867</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>0.5468146471684968</v>
       </c>
       <c r="E94">
-        <v>-30.81531898359978</v>
+        <v>-33.10559697721607</v>
       </c>
       <c r="F94">
-        <v>-6.670275787486489</v>
+        <v>-6.631462718837378</v>
       </c>
       <c r="G94">
-        <v>-5.122775734137501</v>
+        <v>-6.680086150720521</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.05517923426186565</v>
       </c>
       <c r="E95">
-        <v>-32.05172597767701</v>
+        <v>-34.7849725060126</v>
       </c>
       <c r="F95">
-        <v>-6.607637447045507</v>
+        <v>-6.157732727616764</v>
       </c>
       <c r="G95">
-        <v>-5.806631815639211</v>
+        <v>-8.190045834455345</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.6970153267340545</v>
       </c>
       <c r="E96">
-        <v>-34.29402478918203</v>
+        <v>-36.13052704485971</v>
       </c>
       <c r="F96">
-        <v>-6.517128653978142</v>
+        <v>-6.380529663580223</v>
       </c>
       <c r="G96">
-        <v>-6.020228213832987</v>
+        <v>-7.170139585807756</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.363076780468664</v>
       </c>
       <c r="E97">
-        <v>-36.99053407213039</v>
+        <v>-38.55759212435169</v>
       </c>
       <c r="F97">
-        <v>-6.358774691346309</v>
+        <v>-6.38072168792247</v>
       </c>
       <c r="G97">
-        <v>-5.84824206252231</v>
+        <v>-7.274656819028086</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.059270328115216</v>
       </c>
       <c r="E98">
-        <v>-37.85814667149696</v>
+        <v>-39.81357571156408</v>
       </c>
       <c r="F98">
-        <v>-6.568390838902044</v>
+        <v>-6.170042477770997</v>
       </c>
       <c r="G98">
-        <v>-6.869406318474822</v>
+        <v>-8.728737804605553</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.751506000410193</v>
       </c>
       <c r="E99">
-        <v>-41.77328415956845</v>
+        <v>-42.70655736780923</v>
       </c>
       <c r="F99">
-        <v>-6.252649766099755</v>
+        <v>-5.632593266822114</v>
       </c>
       <c r="G99">
-        <v>-6.347128033108321</v>
+        <v>-8.344654932230387</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.455974243325598</v>
       </c>
       <c r="E100">
-        <v>-42.69478107115228</v>
+        <v>-44.70378422296714</v>
       </c>
       <c r="F100">
-        <v>-6.40094957172742</v>
+        <v>-5.939874974477084</v>
       </c>
       <c r="G100">
-        <v>-7.886432392503245</v>
+        <v>-9.076894636788547</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.108590939350607</v>
       </c>
       <c r="E101">
-        <v>-45.88851453590585</v>
+        <v>-47.73337635460169</v>
       </c>
       <c r="F101">
-        <v>-6.489917418939062</v>
+        <v>-5.231442934000174</v>
       </c>
       <c r="G101">
-        <v>-8.106239374128695</v>
+        <v>-9.093904219769321</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.764102780891002</v>
       </c>
       <c r="E102">
-        <v>-48.00669013909763</v>
+        <v>-49.68449881588751</v>
       </c>
       <c r="F102">
-        <v>-6.164831689382722</v>
+        <v>-5.351241576120634</v>
       </c>
       <c r="G102">
-        <v>-7.925129359311786</v>
+        <v>-9.861775325966656</v>
       </c>
     </row>
   </sheetData>
